--- a/outputs/daily/hr_rankings_2026-07-25_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-25_remaining.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -26240,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -28760,7 +28760,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29880,7 +29880,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30440,7 +30440,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -31280,7 +31280,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -32120,7 +32120,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -33520,7 +33520,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -33800,7 +33800,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -34080,7 +34080,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -35200,7 +35200,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -36646,7 +36646,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -39446,7 +39446,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40846,7 +40846,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -41126,7 +41126,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -41406,7 +41406,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -41686,7 +41686,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
